--- a/config/_tables/beans__.xlsx
+++ b/config/_tables/beans__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowWidth="18040" windowHeight="13030"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -93,6 +93,18 @@
   </si>
   <si>
     <t>变体</t>
+  </si>
+  <si>
+    <t>Logic.EffectParamBase</t>
+  </si>
+  <si>
+    <t>Logic.EffectAttack</t>
+  </si>
+  <si>
+    <t>Logic.EffectHurt</t>
+  </si>
+  <si>
+    <t>Logic.EffectInputMove</t>
   </si>
 </sst>
 </file>
@@ -729,7 +741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -744,7 +756,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1068,7 +1079,7 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="28.8181818181818" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="25.5454545454545" customWidth="1"/>
     <col min="10" max="10" width="13.0909090909091" customWidth="1"/>
     <col min="11" max="11" width="47.1818181818182" customWidth="1"/>
     <col min="13" max="13" width="8.09090909090909" customWidth="1"/>
@@ -1189,7 +1200,9 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3"/>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -1207,8 +1220,12 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="5"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1225,126 +1242,138 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:17">
       <c r="A6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
       <c r="Q6"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:17">
       <c r="A9"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
       <c r="Q9"/>
     </row>
     <row r="16" spans="1:17">
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
     </row>
     <row r="22" spans="2:16">
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
     </row>
     <row r="32" spans="2:16">
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
     </row>
     <row r="44" spans="2:16">
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="6"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
     </row>
     <row r="48" spans="2:16">
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="6"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
